--- a/api/1/xlsx/es/SectorGroup.xlsx
+++ b/api/1/xlsx/es/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Educación, nivel no especificado</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Educación</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Educación</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Educación, nivel no especificado</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Educación primaria</t>
   </si>
   <si>
+    <t>Educación básica</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Educación básica</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Educación secundaria superior (modificada, incluye datos de 11322)</t>
   </si>
   <si>
+    <t>Educación secundaria</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Educación secundaria</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Educación superior</t>
   </si>
   <si>
+    <t>Educación post-secundaria</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Educación post-secundaria</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -166,18 +166,18 @@
     <t>Gestión administrativa y políticas de la salud</t>
   </si>
   <si>
+    <t>Salud, general</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Salud</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Salud, general</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>Atención sanitaria básica</t>
   </si>
   <si>
+    <t>Salud básica</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Salud básica</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -259,12 +259,12 @@
     <t>Lucha contra enfermedades no transmisibles, general</t>
   </si>
   <si>
+    <t>Enfermedades no transmisibles</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Enfermedades no transmisibles</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -301,12 +301,12 @@
     <t>Gestión administrativa y políticas en materia demográfica</t>
   </si>
   <si>
+    <t>Programas/políticas sobre población y salud reproductiva</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Programas/políticas sobre población y salud reproductiva</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -337,12 +337,12 @@
     <t>Gestión administrativa y políticas del sector del agua</t>
   </si>
   <si>
+    <t>Abastecimiento de agua y saneamiento</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Abastecimiento de agua y saneamiento</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -409,18 +409,18 @@
     <t>Gestión administrativa y políticas del sector público</t>
   </si>
   <si>
+    <t>Gobierno y sociedad civil, general</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Gobierno y sociedad civil</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Gobierno y sociedad civil</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Gobierno y sociedad civil, general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -517,12 +517,12 @@
     <t>Gestión y reforma del sistema de seguridad</t>
   </si>
   <si>
+    <t>Prevención y resolución de conflictos, paz y seguridad</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Prevención y resolución de conflictos, paz y seguridad</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -559,12 +559,12 @@
     <t>Protección social</t>
   </si>
   <si>
+    <t>Otros servicios e infraestructuras sociales</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Otros servicios e infraestructuras sociales</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>Gestión administrativa y políticas del transporte</t>
   </si>
   <si>
+    <t>Transporte y almacenamiento</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transporte y almacenamiento</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -679,12 +679,12 @@
     <t>Gestión administrativa y políticas de las comunicaciones</t>
   </si>
   <si>
+    <t>Comunicaciones</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Comunicaciones</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -709,18 +709,18 @@
     <t>Gestión administrativa y políticas de la energía</t>
   </si>
   <si>
+    <t>Política energética</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energía</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energía</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Política energética</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Generación de energía, fuentes renovables: múltiples tecnologías</t>
   </si>
   <si>
+    <t>Generación de energía, fuentes renovables</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Generación de energía, fuentes renovables</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -805,12 +805,12 @@
     <t>Generación de energía, fuentes no renovables, sin especificar</t>
   </si>
   <si>
+    <t>Generación de energía, fuentes no renovables</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Generación de energía, fuentes no renovables</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -847,36 +847,36 @@
     <t>Centrales eléctricas de energía híbrida</t>
   </si>
   <si>
+    <t>Centrales de energía híbrida</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Centrales de energía híbrida</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Centrales eléctricas de energía nuclear y seguridad nuclear</t>
   </si>
   <si>
+    <t>Centrales de energía nuclear</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrales de energía nuclear</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Centrales de producción de calor</t>
   </si>
   <si>
+    <t>Distribución de la energía</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribución de la energía</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>Gestión administrativa y políticas financieras</t>
   </si>
   <si>
+    <t>Servicios bancarios y financieros</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Servicios bancarios y financieros</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -961,12 +961,12 @@
     <t>Políticas y administración empresariales</t>
   </si>
   <si>
+    <t>Empresas y otros servicios</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Empresas y otros servicios</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>Gestión administrativa y políticas agrícolas</t>
   </si>
   <si>
+    <t>Agricultura</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agricultura, Silvicultura, Pesca</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agricultura, Silvicultura, Pesca</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agricultura</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1111,12 +1111,12 @@
     <t>Gestión administrativa y políticas forestales</t>
   </si>
   <si>
+    <t>Silvicultura</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Silvicultura</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1153,12 +1153,12 @@
     <t>Gestión administrativa y políticas pesqueras</t>
   </si>
   <si>
+    <t>Pesca</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pesca</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1189,18 +1189,18 @@
     <t>Gestión administrativa y políticas industriales</t>
   </si>
   <si>
+    <t>Industria</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industria, extractivas, construcción</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industria, extractivas, construcción</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industria</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Gestión administrativa y políticas mineras o minerales</t>
   </si>
   <si>
+    <t>Industrias extractivas</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Industrias extractivas</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1381,24 +1381,24 @@
     <t>Gestión administrativa y políticas de la construcción</t>
   </si>
   <si>
+    <t>Construcción</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construcción</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Gestión administrativa y políticas del comercio</t>
   </si>
   <si>
+    <t>Política y regulación comercial</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Política y regulación comercial</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1435,24 +1435,24 @@
     <t>Gestión administrativa y políticas del turismo</t>
   </si>
   <si>
+    <t>Turismo</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Turismo</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Gestión administrativa y políticas del medio ambiente</t>
   </si>
   <si>
+    <t>Protección general medio ambiente</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>Protección general medio ambiente</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1489,12 +1489,12 @@
     <t>Asistencia multisectorial</t>
   </si>
   <si>
+    <t>Otras acciones multisectoriales</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Otras acciones multisectoriales</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1555,36 +1555,36 @@
     <t>Asistencia relacionada con el apoyo presupuestario general</t>
   </si>
   <si>
+    <t>Apoyo presupuestario general</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>Apoyo presupuestario general</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Asistencia alimentaria</t>
   </si>
   <si>
+    <t>Ayuda alimentaria para el desarrollo</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Ayuda alimentaria para el desarrollo</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Apoyo a importaciones (bienes de capital)</t>
   </si>
   <si>
+    <t>Otras ayudas en forma de suministro de bienes</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Otras ayudas en forma de suministro de bienes</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1597,12 +1597,12 @@
     <t>Acciones relativas a la deuda</t>
   </si>
   <si>
+    <t>Actividades relacionadas con la deuda</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Actividades relacionadas con la deuda</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1645,12 +1645,12 @@
     <t>Asistencia y servicios de socorro material</t>
   </si>
   <si>
+    <t>Ayuda de emergencia</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Ayuda de emergencia</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1669,58 +1669,58 @@
     <t>Reconstrucción y rehabilitación inmediata posemergencias</t>
   </si>
   <si>
+    <t>Ayuda a la reconstrucción y a la rehabilitación</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Ayuda a la reconstrucción y a la rehabilitación</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Preparación de respuesta multirriesgos</t>
   </si>
   <si>
+    <t>Prevención de desastres</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Prevención de desastres</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Costos administrativos (no asignable por sectores)</t>
   </si>
   <si>
+    <t>Costes administrativos donantes</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Costes administrativos donantes</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugiados o solicitantes de asilo en países donantes (no asignable por sectores)</t>
   </si>
   <si>
+    <t>Ayuda a refugiados en el país donante</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Ayuda a refugiados en el país donante</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectores no especificados</t>
   </si>
   <si>
+    <t>Sin especificación / no clasificados</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Sin especificación / no clasificados</t>
   </si>
   <si>
     <t>99820</t>

--- a/api/1/xlsx/es/SectorGroup.xlsx
+++ b/api/1/xlsx/es/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Educación, nivel no especificado</t>
   </si>
   <si>
+    <t>Educación</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Educación</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>Salud, general</t>
   </si>
   <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Salud</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -412,15 +412,15 @@
     <t>Gobierno y sociedad civil, general</t>
   </si>
   <si>
+    <t>Gobierno y sociedad civil</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Gobierno y sociedad civil</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -712,15 +712,15 @@
     <t>Política energética</t>
   </si>
   <si>
+    <t>Energía</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energía</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>Agricultura</t>
   </si>
   <si>
+    <t>Agricultura, Silvicultura, Pesca</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agricultura, Silvicultura, Pesca</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1192,13 +1192,13 @@
     <t>Industria</t>
   </si>
   <si>
+    <t>Industria, extractivas, construcción</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industria, extractivas, construcción</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2193,10 +2193,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2216,10 +2216,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2239,10 +2239,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2262,10 +2262,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2285,10 +2285,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2308,10 +2308,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2331,10 +2331,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2354,10 +2354,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2377,10 +2377,10 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2400,10 +2400,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2423,10 +2423,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2538,10 +2538,10 @@
         <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2561,10 +2561,10 @@
         <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2584,10 +2584,10 @@
         <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2607,10 +2607,10 @@
         <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2630,10 +2630,10 @@
         <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2653,10 +2653,10 @@
         <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2676,10 +2676,10 @@
         <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2696,10 +2696,10 @@
         <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2719,10 +2719,10 @@
         <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2742,10 +2742,10 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2765,10 +2765,10 @@
         <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2788,10 +2788,10 @@
         <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2811,10 +2811,10 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2834,10 +2834,10 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2857,10 +2857,10 @@
         <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2877,10 +2877,10 @@
         <v>95</v>
       </c>
       <c r="E36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" t="s">
         <v>96</v>
-      </c>
-      <c r="F36" t="s">
-        <v>95</v>
       </c>
       <c r="G36" t="s">
         <v>96</v>
@@ -2900,10 +2900,10 @@
         <v>95</v>
       </c>
       <c r="E37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" t="s">
         <v>96</v>
-      </c>
-      <c r="F37" t="s">
-        <v>95</v>
       </c>
       <c r="G37" t="s">
         <v>96</v>
@@ -2923,10 +2923,10 @@
         <v>95</v>
       </c>
       <c r="E38" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" t="s">
         <v>96</v>
-      </c>
-      <c r="F38" t="s">
-        <v>95</v>
       </c>
       <c r="G38" t="s">
         <v>96</v>
@@ -2946,10 +2946,10 @@
         <v>95</v>
       </c>
       <c r="E39" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" t="s">
         <v>96</v>
-      </c>
-      <c r="F39" t="s">
-        <v>95</v>
       </c>
       <c r="G39" t="s">
         <v>96</v>
@@ -2969,10 +2969,10 @@
         <v>95</v>
       </c>
       <c r="E40" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" t="s">
         <v>96</v>
-      </c>
-      <c r="F40" t="s">
-        <v>95</v>
       </c>
       <c r="G40" t="s">
         <v>96</v>
@@ -2992,10 +2992,10 @@
         <v>107</v>
       </c>
       <c r="E41" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" t="s">
         <v>108</v>
-      </c>
-      <c r="F41" t="s">
-        <v>107</v>
       </c>
       <c r="G41" t="s">
         <v>108</v>
@@ -3015,10 +3015,10 @@
         <v>107</v>
       </c>
       <c r="E42" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" t="s">
         <v>108</v>
-      </c>
-      <c r="F42" t="s">
-        <v>107</v>
       </c>
       <c r="G42" t="s">
         <v>108</v>
@@ -3038,10 +3038,10 @@
         <v>107</v>
       </c>
       <c r="E43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" t="s">
         <v>108</v>
-      </c>
-      <c r="F43" t="s">
-        <v>107</v>
       </c>
       <c r="G43" t="s">
         <v>108</v>
@@ -3061,10 +3061,10 @@
         <v>107</v>
       </c>
       <c r="E44" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" t="s">
         <v>108</v>
-      </c>
-      <c r="F44" t="s">
-        <v>107</v>
       </c>
       <c r="G44" t="s">
         <v>108</v>
@@ -3084,10 +3084,10 @@
         <v>107</v>
       </c>
       <c r="E45" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" t="s">
         <v>108</v>
-      </c>
-      <c r="F45" t="s">
-        <v>107</v>
       </c>
       <c r="G45" t="s">
         <v>108</v>
@@ -3107,10 +3107,10 @@
         <v>107</v>
       </c>
       <c r="E46" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" t="s">
         <v>108</v>
-      </c>
-      <c r="F46" t="s">
-        <v>107</v>
       </c>
       <c r="G46" t="s">
         <v>108</v>
@@ -3130,10 +3130,10 @@
         <v>107</v>
       </c>
       <c r="E47" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" t="s">
         <v>108</v>
-      </c>
-      <c r="F47" t="s">
-        <v>107</v>
       </c>
       <c r="G47" t="s">
         <v>108</v>
@@ -3153,10 +3153,10 @@
         <v>107</v>
       </c>
       <c r="E48" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" t="s">
         <v>108</v>
-      </c>
-      <c r="F48" t="s">
-        <v>107</v>
       </c>
       <c r="G48" t="s">
         <v>108</v>
@@ -3176,10 +3176,10 @@
         <v>107</v>
       </c>
       <c r="E49" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" t="s">
         <v>108</v>
-      </c>
-      <c r="F49" t="s">
-        <v>107</v>
       </c>
       <c r="G49" t="s">
         <v>108</v>
@@ -3199,10 +3199,10 @@
         <v>107</v>
       </c>
       <c r="E50" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" t="s">
         <v>108</v>
-      </c>
-      <c r="F50" t="s">
-        <v>107</v>
       </c>
       <c r="G50" t="s">
         <v>108</v>
@@ -3222,10 +3222,10 @@
         <v>107</v>
       </c>
       <c r="E51" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" t="s">
         <v>108</v>
-      </c>
-      <c r="F51" t="s">
-        <v>107</v>
       </c>
       <c r="G51" t="s">
         <v>108</v>
@@ -3616,10 +3616,10 @@
         <v>132</v>
       </c>
       <c r="F68" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G68" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3639,10 +3639,10 @@
         <v>132</v>
       </c>
       <c r="F69" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G69" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3662,10 +3662,10 @@
         <v>132</v>
       </c>
       <c r="F70" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G70" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3685,10 +3685,10 @@
         <v>132</v>
       </c>
       <c r="F71" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G71" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3708,10 +3708,10 @@
         <v>132</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G72" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3731,10 +3731,10 @@
         <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="G73" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3751,10 +3751,10 @@
         <v>181</v>
       </c>
       <c r="E74" t="s">
+        <v>181</v>
+      </c>
+      <c r="F74" t="s">
         <v>182</v>
-      </c>
-      <c r="F74" t="s">
-        <v>181</v>
       </c>
       <c r="G74" t="s">
         <v>182</v>
@@ -3774,10 +3774,10 @@
         <v>181</v>
       </c>
       <c r="E75" t="s">
+        <v>181</v>
+      </c>
+      <c r="F75" t="s">
         <v>182</v>
-      </c>
-      <c r="F75" t="s">
-        <v>181</v>
       </c>
       <c r="G75" t="s">
         <v>182</v>
@@ -3797,10 +3797,10 @@
         <v>181</v>
       </c>
       <c r="E76" t="s">
+        <v>181</v>
+      </c>
+      <c r="F76" t="s">
         <v>182</v>
-      </c>
-      <c r="F76" t="s">
-        <v>181</v>
       </c>
       <c r="G76" t="s">
         <v>182</v>
@@ -3820,10 +3820,10 @@
         <v>181</v>
       </c>
       <c r="E77" t="s">
+        <v>181</v>
+      </c>
+      <c r="F77" t="s">
         <v>182</v>
-      </c>
-      <c r="F77" t="s">
-        <v>181</v>
       </c>
       <c r="G77" t="s">
         <v>182</v>
@@ -3843,10 +3843,10 @@
         <v>181</v>
       </c>
       <c r="E78" t="s">
+        <v>181</v>
+      </c>
+      <c r="F78" t="s">
         <v>182</v>
-      </c>
-      <c r="F78" t="s">
-        <v>181</v>
       </c>
       <c r="G78" t="s">
         <v>182</v>
@@ -3866,10 +3866,10 @@
         <v>181</v>
       </c>
       <c r="E79" t="s">
+        <v>181</v>
+      </c>
+      <c r="F79" t="s">
         <v>182</v>
-      </c>
-      <c r="F79" t="s">
-        <v>181</v>
       </c>
       <c r="G79" t="s">
         <v>182</v>
@@ -3889,10 +3889,10 @@
         <v>181</v>
       </c>
       <c r="E80" t="s">
+        <v>181</v>
+      </c>
+      <c r="F80" t="s">
         <v>182</v>
-      </c>
-      <c r="F80" t="s">
-        <v>181</v>
       </c>
       <c r="G80" t="s">
         <v>182</v>
@@ -3912,10 +3912,10 @@
         <v>181</v>
       </c>
       <c r="E81" t="s">
+        <v>181</v>
+      </c>
+      <c r="F81" t="s">
         <v>182</v>
-      </c>
-      <c r="F81" t="s">
-        <v>181</v>
       </c>
       <c r="G81" t="s">
         <v>182</v>
@@ -3935,10 +3935,10 @@
         <v>181</v>
       </c>
       <c r="E82" t="s">
+        <v>181</v>
+      </c>
+      <c r="F82" t="s">
         <v>182</v>
-      </c>
-      <c r="F82" t="s">
-        <v>181</v>
       </c>
       <c r="G82" t="s">
         <v>182</v>
@@ -3958,10 +3958,10 @@
         <v>181</v>
       </c>
       <c r="E83" t="s">
+        <v>181</v>
+      </c>
+      <c r="F83" t="s">
         <v>182</v>
-      </c>
-      <c r="F83" t="s">
-        <v>181</v>
       </c>
       <c r="G83" t="s">
         <v>182</v>
@@ -3981,10 +3981,10 @@
         <v>181</v>
       </c>
       <c r="E84" t="s">
+        <v>181</v>
+      </c>
+      <c r="F84" t="s">
         <v>182</v>
-      </c>
-      <c r="F84" t="s">
-        <v>181</v>
       </c>
       <c r="G84" t="s">
         <v>182</v>
@@ -4004,10 +4004,10 @@
         <v>205</v>
       </c>
       <c r="E85" t="s">
+        <v>205</v>
+      </c>
+      <c r="F85" t="s">
         <v>206</v>
-      </c>
-      <c r="F85" t="s">
-        <v>205</v>
       </c>
       <c r="G85" t="s">
         <v>206</v>
@@ -4027,10 +4027,10 @@
         <v>205</v>
       </c>
       <c r="E86" t="s">
+        <v>205</v>
+      </c>
+      <c r="F86" t="s">
         <v>206</v>
-      </c>
-      <c r="F86" t="s">
-        <v>205</v>
       </c>
       <c r="G86" t="s">
         <v>206</v>
@@ -4050,10 +4050,10 @@
         <v>205</v>
       </c>
       <c r="E87" t="s">
+        <v>205</v>
+      </c>
+      <c r="F87" t="s">
         <v>206</v>
-      </c>
-      <c r="F87" t="s">
-        <v>205</v>
       </c>
       <c r="G87" t="s">
         <v>206</v>
@@ -4073,10 +4073,10 @@
         <v>205</v>
       </c>
       <c r="E88" t="s">
+        <v>205</v>
+      </c>
+      <c r="F88" t="s">
         <v>206</v>
-      </c>
-      <c r="F88" t="s">
-        <v>205</v>
       </c>
       <c r="G88" t="s">
         <v>206</v>
@@ -4096,10 +4096,10 @@
         <v>205</v>
       </c>
       <c r="E89" t="s">
+        <v>205</v>
+      </c>
+      <c r="F89" t="s">
         <v>206</v>
-      </c>
-      <c r="F89" t="s">
-        <v>205</v>
       </c>
       <c r="G89" t="s">
         <v>206</v>
@@ -4119,10 +4119,10 @@
         <v>205</v>
       </c>
       <c r="E90" t="s">
+        <v>205</v>
+      </c>
+      <c r="F90" t="s">
         <v>206</v>
-      </c>
-      <c r="F90" t="s">
-        <v>205</v>
       </c>
       <c r="G90" t="s">
         <v>206</v>
@@ -4142,10 +4142,10 @@
         <v>205</v>
       </c>
       <c r="E91" t="s">
+        <v>205</v>
+      </c>
+      <c r="F91" t="s">
         <v>206</v>
-      </c>
-      <c r="F91" t="s">
-        <v>205</v>
       </c>
       <c r="G91" t="s">
         <v>206</v>
@@ -4165,10 +4165,10 @@
         <v>221</v>
       </c>
       <c r="E92" t="s">
+        <v>221</v>
+      </c>
+      <c r="F92" t="s">
         <v>222</v>
-      </c>
-      <c r="F92" t="s">
-        <v>221</v>
       </c>
       <c r="G92" t="s">
         <v>222</v>
@@ -4188,10 +4188,10 @@
         <v>221</v>
       </c>
       <c r="E93" t="s">
+        <v>221</v>
+      </c>
+      <c r="F93" t="s">
         <v>222</v>
-      </c>
-      <c r="F93" t="s">
-        <v>221</v>
       </c>
       <c r="G93" t="s">
         <v>222</v>
@@ -4211,10 +4211,10 @@
         <v>221</v>
       </c>
       <c r="E94" t="s">
+        <v>221</v>
+      </c>
+      <c r="F94" t="s">
         <v>222</v>
-      </c>
-      <c r="F94" t="s">
-        <v>221</v>
       </c>
       <c r="G94" t="s">
         <v>222</v>
@@ -4234,10 +4234,10 @@
         <v>221</v>
       </c>
       <c r="E95" t="s">
+        <v>221</v>
+      </c>
+      <c r="F95" t="s">
         <v>222</v>
-      </c>
-      <c r="F95" t="s">
-        <v>221</v>
       </c>
       <c r="G95" t="s">
         <v>222</v>
@@ -4352,10 +4352,10 @@
         <v>232</v>
       </c>
       <c r="F100" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G100" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4375,10 +4375,10 @@
         <v>232</v>
       </c>
       <c r="F101" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G101" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4398,10 +4398,10 @@
         <v>232</v>
       </c>
       <c r="F102" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G102" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4421,10 +4421,10 @@
         <v>232</v>
       </c>
       <c r="F103" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G103" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4444,10 +4444,10 @@
         <v>232</v>
       </c>
       <c r="F104" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G104" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4467,10 +4467,10 @@
         <v>232</v>
       </c>
       <c r="F105" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G105" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4490,10 +4490,10 @@
         <v>232</v>
       </c>
       <c r="F106" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G106" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4513,10 +4513,10 @@
         <v>232</v>
       </c>
       <c r="F107" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G107" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4536,10 +4536,10 @@
         <v>232</v>
       </c>
       <c r="F108" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G108" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4559,10 +4559,10 @@
         <v>232</v>
       </c>
       <c r="F109" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G109" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4582,10 +4582,10 @@
         <v>232</v>
       </c>
       <c r="F110" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G110" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4605,10 +4605,10 @@
         <v>232</v>
       </c>
       <c r="F111" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G111" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4628,10 +4628,10 @@
         <v>232</v>
       </c>
       <c r="F112" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G112" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4651,10 +4651,10 @@
         <v>232</v>
       </c>
       <c r="F113" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G113" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4674,10 +4674,10 @@
         <v>232</v>
       </c>
       <c r="F114" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="G114" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4697,10 +4697,10 @@
         <v>232</v>
       </c>
       <c r="F115" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="G115" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4720,10 +4720,10 @@
         <v>232</v>
       </c>
       <c r="F116" t="s">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="G116" t="s">
-        <v>282</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4743,10 +4743,10 @@
         <v>232</v>
       </c>
       <c r="F117" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G117" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4766,10 +4766,10 @@
         <v>232</v>
       </c>
       <c r="F118" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G118" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4789,10 +4789,10 @@
         <v>232</v>
       </c>
       <c r="F119" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G119" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4812,10 +4812,10 @@
         <v>232</v>
       </c>
       <c r="F120" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G120" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>232</v>
       </c>
       <c r="F121" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G121" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4858,10 +4858,10 @@
         <v>232</v>
       </c>
       <c r="F122" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G122" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4881,10 +4881,10 @@
         <v>232</v>
       </c>
       <c r="F123" t="s">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="G123" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4901,10 +4901,10 @@
         <v>301</v>
       </c>
       <c r="E124" t="s">
+        <v>301</v>
+      </c>
+      <c r="F124" t="s">
         <v>302</v>
-      </c>
-      <c r="F124" t="s">
-        <v>301</v>
       </c>
       <c r="G124" t="s">
         <v>302</v>
@@ -4924,10 +4924,10 @@
         <v>301</v>
       </c>
       <c r="E125" t="s">
+        <v>301</v>
+      </c>
+      <c r="F125" t="s">
         <v>302</v>
-      </c>
-      <c r="F125" t="s">
-        <v>301</v>
       </c>
       <c r="G125" t="s">
         <v>302</v>
@@ -4947,10 +4947,10 @@
         <v>301</v>
       </c>
       <c r="E126" t="s">
+        <v>301</v>
+      </c>
+      <c r="F126" t="s">
         <v>302</v>
-      </c>
-      <c r="F126" t="s">
-        <v>301</v>
       </c>
       <c r="G126" t="s">
         <v>302</v>
@@ -4970,10 +4970,10 @@
         <v>301</v>
       </c>
       <c r="E127" t="s">
+        <v>301</v>
+      </c>
+      <c r="F127" t="s">
         <v>302</v>
-      </c>
-      <c r="F127" t="s">
-        <v>301</v>
       </c>
       <c r="G127" t="s">
         <v>302</v>
@@ -4993,10 +4993,10 @@
         <v>301</v>
       </c>
       <c r="E128" t="s">
+        <v>301</v>
+      </c>
+      <c r="F128" t="s">
         <v>302</v>
-      </c>
-      <c r="F128" t="s">
-        <v>301</v>
       </c>
       <c r="G128" t="s">
         <v>302</v>
@@ -5016,10 +5016,10 @@
         <v>301</v>
       </c>
       <c r="E129" t="s">
+        <v>301</v>
+      </c>
+      <c r="F129" t="s">
         <v>302</v>
-      </c>
-      <c r="F129" t="s">
-        <v>301</v>
       </c>
       <c r="G129" t="s">
         <v>302</v>
@@ -5039,10 +5039,10 @@
         <v>315</v>
       </c>
       <c r="E130" t="s">
+        <v>315</v>
+      </c>
+      <c r="F130" t="s">
         <v>316</v>
-      </c>
-      <c r="F130" t="s">
-        <v>315</v>
       </c>
       <c r="G130" t="s">
         <v>316</v>
@@ -5062,10 +5062,10 @@
         <v>315</v>
       </c>
       <c r="E131" t="s">
+        <v>315</v>
+      </c>
+      <c r="F131" t="s">
         <v>316</v>
-      </c>
-      <c r="F131" t="s">
-        <v>315</v>
       </c>
       <c r="G131" t="s">
         <v>316</v>
@@ -5085,10 +5085,10 @@
         <v>315</v>
       </c>
       <c r="E132" t="s">
+        <v>315</v>
+      </c>
+      <c r="F132" t="s">
         <v>316</v>
-      </c>
-      <c r="F132" t="s">
-        <v>315</v>
       </c>
       <c r="G132" t="s">
         <v>316</v>
@@ -5108,10 +5108,10 @@
         <v>315</v>
       </c>
       <c r="E133" t="s">
+        <v>315</v>
+      </c>
+      <c r="F133" t="s">
         <v>316</v>
-      </c>
-      <c r="F133" t="s">
-        <v>315</v>
       </c>
       <c r="G133" t="s">
         <v>316</v>
@@ -5548,10 +5548,10 @@
         <v>326</v>
       </c>
       <c r="F152" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G152" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5571,10 +5571,10 @@
         <v>326</v>
       </c>
       <c r="F153" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G153" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5594,10 +5594,10 @@
         <v>326</v>
       </c>
       <c r="F154" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G154" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5617,10 +5617,10 @@
         <v>326</v>
       </c>
       <c r="F155" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G155" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5640,10 +5640,10 @@
         <v>326</v>
       </c>
       <c r="F156" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G156" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5663,10 +5663,10 @@
         <v>326</v>
       </c>
       <c r="F157" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="G157" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5686,10 +5686,10 @@
         <v>326</v>
       </c>
       <c r="F158" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G158" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5709,10 +5709,10 @@
         <v>326</v>
       </c>
       <c r="F159" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G159" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5732,10 +5732,10 @@
         <v>326</v>
       </c>
       <c r="F160" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G160" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5755,10 +5755,10 @@
         <v>326</v>
       </c>
       <c r="F161" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G161" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5778,10 +5778,10 @@
         <v>326</v>
       </c>
       <c r="F162" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="G162" t="s">
-        <v>380</v>
+        <v>328</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6238,10 +6238,10 @@
         <v>392</v>
       </c>
       <c r="F182" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G182" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6261,10 +6261,10 @@
         <v>392</v>
       </c>
       <c r="F183" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G183" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6284,10 +6284,10 @@
         <v>392</v>
       </c>
       <c r="F184" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G184" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6307,10 +6307,10 @@
         <v>392</v>
       </c>
       <c r="F185" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G185" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6330,10 +6330,10 @@
         <v>392</v>
       </c>
       <c r="F186" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G186" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6353,10 +6353,10 @@
         <v>392</v>
       </c>
       <c r="F187" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G187" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6376,10 +6376,10 @@
         <v>392</v>
       </c>
       <c r="F188" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G188" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6399,10 +6399,10 @@
         <v>392</v>
       </c>
       <c r="F189" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G189" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6422,10 +6422,10 @@
         <v>392</v>
       </c>
       <c r="F190" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G190" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6445,10 +6445,10 @@
         <v>392</v>
       </c>
       <c r="F191" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="G191" t="s">
-        <v>434</v>
+        <v>394</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6468,10 +6468,10 @@
         <v>392</v>
       </c>
       <c r="F192" t="s">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="G192" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6488,10 +6488,10 @@
         <v>459</v>
       </c>
       <c r="E193" t="s">
+        <v>459</v>
+      </c>
+      <c r="F193" t="s">
         <v>460</v>
-      </c>
-      <c r="F193" t="s">
-        <v>459</v>
       </c>
       <c r="G193" t="s">
         <v>460</v>
@@ -6511,10 +6511,10 @@
         <v>459</v>
       </c>
       <c r="E194" t="s">
+        <v>459</v>
+      </c>
+      <c r="F194" t="s">
         <v>460</v>
-      </c>
-      <c r="F194" t="s">
-        <v>459</v>
       </c>
       <c r="G194" t="s">
         <v>460</v>
@@ -6534,10 +6534,10 @@
         <v>459</v>
       </c>
       <c r="E195" t="s">
+        <v>459</v>
+      </c>
+      <c r="F195" t="s">
         <v>460</v>
-      </c>
-      <c r="F195" t="s">
-        <v>459</v>
       </c>
       <c r="G195" t="s">
         <v>460</v>
@@ -6557,10 +6557,10 @@
         <v>459</v>
       </c>
       <c r="E196" t="s">
+        <v>459</v>
+      </c>
+      <c r="F196" t="s">
         <v>460</v>
-      </c>
-      <c r="F196" t="s">
-        <v>459</v>
       </c>
       <c r="G196" t="s">
         <v>460</v>
@@ -6580,10 +6580,10 @@
         <v>459</v>
       </c>
       <c r="E197" t="s">
+        <v>459</v>
+      </c>
+      <c r="F197" t="s">
         <v>460</v>
-      </c>
-      <c r="F197" t="s">
-        <v>459</v>
       </c>
       <c r="G197" t="s">
         <v>460</v>
@@ -6603,10 +6603,10 @@
         <v>459</v>
       </c>
       <c r="E198" t="s">
+        <v>459</v>
+      </c>
+      <c r="F198" t="s">
         <v>460</v>
-      </c>
-      <c r="F198" t="s">
-        <v>459</v>
       </c>
       <c r="G198" t="s">
         <v>460</v>
@@ -6626,10 +6626,10 @@
         <v>473</v>
       </c>
       <c r="E199" t="s">
+        <v>473</v>
+      </c>
+      <c r="F199" t="s">
         <v>474</v>
-      </c>
-      <c r="F199" t="s">
-        <v>473</v>
       </c>
       <c r="G199" t="s">
         <v>474</v>
@@ -6649,10 +6649,10 @@
         <v>477</v>
       </c>
       <c r="E200" t="s">
+        <v>477</v>
+      </c>
+      <c r="F200" t="s">
         <v>478</v>
-      </c>
-      <c r="F200" t="s">
-        <v>477</v>
       </c>
       <c r="G200" t="s">
         <v>478</v>
@@ -6672,10 +6672,10 @@
         <v>477</v>
       </c>
       <c r="E201" t="s">
+        <v>477</v>
+      </c>
+      <c r="F201" t="s">
         <v>478</v>
-      </c>
-      <c r="F201" t="s">
-        <v>477</v>
       </c>
       <c r="G201" t="s">
         <v>478</v>
@@ -6695,10 +6695,10 @@
         <v>477</v>
       </c>
       <c r="E202" t="s">
+        <v>477</v>
+      </c>
+      <c r="F202" t="s">
         <v>478</v>
-      </c>
-      <c r="F202" t="s">
-        <v>477</v>
       </c>
       <c r="G202" t="s">
         <v>478</v>
@@ -6718,10 +6718,10 @@
         <v>477</v>
       </c>
       <c r="E203" t="s">
+        <v>477</v>
+      </c>
+      <c r="F203" t="s">
         <v>478</v>
-      </c>
-      <c r="F203" t="s">
-        <v>477</v>
       </c>
       <c r="G203" t="s">
         <v>478</v>
@@ -6741,10 +6741,10 @@
         <v>477</v>
       </c>
       <c r="E204" t="s">
+        <v>477</v>
+      </c>
+      <c r="F204" t="s">
         <v>478</v>
-      </c>
-      <c r="F204" t="s">
-        <v>477</v>
       </c>
       <c r="G204" t="s">
         <v>478</v>
@@ -6764,10 +6764,10 @@
         <v>477</v>
       </c>
       <c r="E205" t="s">
+        <v>477</v>
+      </c>
+      <c r="F205" t="s">
         <v>478</v>
-      </c>
-      <c r="F205" t="s">
-        <v>477</v>
       </c>
       <c r="G205" t="s">
         <v>478</v>
@@ -6787,10 +6787,10 @@
         <v>491</v>
       </c>
       <c r="E206" t="s">
+        <v>491</v>
+      </c>
+      <c r="F206" t="s">
         <v>492</v>
-      </c>
-      <c r="F206" t="s">
-        <v>491</v>
       </c>
       <c r="G206" t="s">
         <v>492</v>
@@ -6810,10 +6810,10 @@
         <v>491</v>
       </c>
       <c r="E207" t="s">
+        <v>491</v>
+      </c>
+      <c r="F207" t="s">
         <v>492</v>
-      </c>
-      <c r="F207" t="s">
-        <v>491</v>
       </c>
       <c r="G207" t="s">
         <v>492</v>
@@ -6833,10 +6833,10 @@
         <v>491</v>
       </c>
       <c r="E208" t="s">
+        <v>491</v>
+      </c>
+      <c r="F208" t="s">
         <v>492</v>
-      </c>
-      <c r="F208" t="s">
-        <v>491</v>
       </c>
       <c r="G208" t="s">
         <v>492</v>
@@ -6856,10 +6856,10 @@
         <v>491</v>
       </c>
       <c r="E209" t="s">
+        <v>491</v>
+      </c>
+      <c r="F209" t="s">
         <v>492</v>
-      </c>
-      <c r="F209" t="s">
-        <v>491</v>
       </c>
       <c r="G209" t="s">
         <v>492</v>
@@ -6879,10 +6879,10 @@
         <v>491</v>
       </c>
       <c r="E210" t="s">
+        <v>491</v>
+      </c>
+      <c r="F210" t="s">
         <v>492</v>
-      </c>
-      <c r="F210" t="s">
-        <v>491</v>
       </c>
       <c r="G210" t="s">
         <v>492</v>
@@ -6902,10 +6902,10 @@
         <v>491</v>
       </c>
       <c r="E211" t="s">
+        <v>491</v>
+      </c>
+      <c r="F211" t="s">
         <v>492</v>
-      </c>
-      <c r="F211" t="s">
-        <v>491</v>
       </c>
       <c r="G211" t="s">
         <v>492</v>
@@ -6925,10 +6925,10 @@
         <v>491</v>
       </c>
       <c r="E212" t="s">
+        <v>491</v>
+      </c>
+      <c r="F212" t="s">
         <v>492</v>
-      </c>
-      <c r="F212" t="s">
-        <v>491</v>
       </c>
       <c r="G212" t="s">
         <v>492</v>
@@ -6948,10 +6948,10 @@
         <v>491</v>
       </c>
       <c r="E213" t="s">
+        <v>491</v>
+      </c>
+      <c r="F213" t="s">
         <v>492</v>
-      </c>
-      <c r="F213" t="s">
-        <v>491</v>
       </c>
       <c r="G213" t="s">
         <v>492</v>
@@ -6971,10 +6971,10 @@
         <v>491</v>
       </c>
       <c r="E214" t="s">
+        <v>491</v>
+      </c>
+      <c r="F214" t="s">
         <v>492</v>
-      </c>
-      <c r="F214" t="s">
-        <v>491</v>
       </c>
       <c r="G214" t="s">
         <v>492</v>
@@ -6994,10 +6994,10 @@
         <v>491</v>
       </c>
       <c r="E215" t="s">
+        <v>491</v>
+      </c>
+      <c r="F215" t="s">
         <v>492</v>
-      </c>
-      <c r="F215" t="s">
-        <v>491</v>
       </c>
       <c r="G215" t="s">
         <v>492</v>
@@ -7017,10 +7017,10 @@
         <v>513</v>
       </c>
       <c r="E216" t="s">
+        <v>513</v>
+      </c>
+      <c r="F216" t="s">
         <v>514</v>
-      </c>
-      <c r="F216" t="s">
-        <v>513</v>
       </c>
       <c r="G216" t="s">
         <v>514</v>
@@ -7040,10 +7040,10 @@
         <v>517</v>
       </c>
       <c r="E217" t="s">
+        <v>517</v>
+      </c>
+      <c r="F217" t="s">
         <v>518</v>
-      </c>
-      <c r="F217" t="s">
-        <v>517</v>
       </c>
       <c r="G217" t="s">
         <v>518</v>
@@ -7063,10 +7063,10 @@
         <v>521</v>
       </c>
       <c r="E218" t="s">
+        <v>521</v>
+      </c>
+      <c r="F218" t="s">
         <v>522</v>
-      </c>
-      <c r="F218" t="s">
-        <v>521</v>
       </c>
       <c r="G218" t="s">
         <v>522</v>
@@ -7086,10 +7086,10 @@
         <v>521</v>
       </c>
       <c r="E219" t="s">
+        <v>521</v>
+      </c>
+      <c r="F219" t="s">
         <v>522</v>
-      </c>
-      <c r="F219" t="s">
-        <v>521</v>
       </c>
       <c r="G219" t="s">
         <v>522</v>
@@ -7109,10 +7109,10 @@
         <v>527</v>
       </c>
       <c r="E220" t="s">
+        <v>527</v>
+      </c>
+      <c r="F220" t="s">
         <v>528</v>
-      </c>
-      <c r="F220" t="s">
-        <v>527</v>
       </c>
       <c r="G220" t="s">
         <v>528</v>
@@ -7132,10 +7132,10 @@
         <v>527</v>
       </c>
       <c r="E221" t="s">
+        <v>527</v>
+      </c>
+      <c r="F221" t="s">
         <v>528</v>
-      </c>
-      <c r="F221" t="s">
-        <v>527</v>
       </c>
       <c r="G221" t="s">
         <v>528</v>
@@ -7155,10 +7155,10 @@
         <v>527</v>
       </c>
       <c r="E222" t="s">
+        <v>527</v>
+      </c>
+      <c r="F222" t="s">
         <v>528</v>
-      </c>
-      <c r="F222" t="s">
-        <v>527</v>
       </c>
       <c r="G222" t="s">
         <v>528</v>
@@ -7178,10 +7178,10 @@
         <v>527</v>
       </c>
       <c r="E223" t="s">
+        <v>527</v>
+      </c>
+      <c r="F223" t="s">
         <v>528</v>
-      </c>
-      <c r="F223" t="s">
-        <v>527</v>
       </c>
       <c r="G223" t="s">
         <v>528</v>
@@ -7201,10 +7201,10 @@
         <v>527</v>
       </c>
       <c r="E224" t="s">
+        <v>527</v>
+      </c>
+      <c r="F224" t="s">
         <v>528</v>
-      </c>
-      <c r="F224" t="s">
-        <v>527</v>
       </c>
       <c r="G224" t="s">
         <v>528</v>
@@ -7224,10 +7224,10 @@
         <v>527</v>
       </c>
       <c r="E225" t="s">
+        <v>527</v>
+      </c>
+      <c r="F225" t="s">
         <v>528</v>
-      </c>
-      <c r="F225" t="s">
-        <v>527</v>
       </c>
       <c r="G225" t="s">
         <v>528</v>
@@ -7247,10 +7247,10 @@
         <v>527</v>
       </c>
       <c r="E226" t="s">
+        <v>527</v>
+      </c>
+      <c r="F226" t="s">
         <v>528</v>
-      </c>
-      <c r="F226" t="s">
-        <v>527</v>
       </c>
       <c r="G226" t="s">
         <v>528</v>
@@ -7270,10 +7270,10 @@
         <v>543</v>
       </c>
       <c r="E227" t="s">
+        <v>543</v>
+      </c>
+      <c r="F227" t="s">
         <v>544</v>
-      </c>
-      <c r="F227" t="s">
-        <v>543</v>
       </c>
       <c r="G227" t="s">
         <v>544</v>
@@ -7293,10 +7293,10 @@
         <v>543</v>
       </c>
       <c r="E228" t="s">
+        <v>543</v>
+      </c>
+      <c r="F228" t="s">
         <v>544</v>
-      </c>
-      <c r="F228" t="s">
-        <v>543</v>
       </c>
       <c r="G228" t="s">
         <v>544</v>
@@ -7316,10 +7316,10 @@
         <v>543</v>
       </c>
       <c r="E229" t="s">
+        <v>543</v>
+      </c>
+      <c r="F229" t="s">
         <v>544</v>
-      </c>
-      <c r="F229" t="s">
-        <v>543</v>
       </c>
       <c r="G229" t="s">
         <v>544</v>
@@ -7339,10 +7339,10 @@
         <v>551</v>
       </c>
       <c r="E230" t="s">
+        <v>551</v>
+      </c>
+      <c r="F230" t="s">
         <v>552</v>
-      </c>
-      <c r="F230" t="s">
-        <v>551</v>
       </c>
       <c r="G230" t="s">
         <v>552</v>
@@ -7362,10 +7362,10 @@
         <v>555</v>
       </c>
       <c r="E231" t="s">
+        <v>555</v>
+      </c>
+      <c r="F231" t="s">
         <v>556</v>
-      </c>
-      <c r="F231" t="s">
-        <v>555</v>
       </c>
       <c r="G231" t="s">
         <v>556</v>
@@ -7385,10 +7385,10 @@
         <v>559</v>
       </c>
       <c r="E232" t="s">
+        <v>559</v>
+      </c>
+      <c r="F232" t="s">
         <v>560</v>
-      </c>
-      <c r="F232" t="s">
-        <v>559</v>
       </c>
       <c r="G232" t="s">
         <v>560</v>
@@ -7408,10 +7408,10 @@
         <v>563</v>
       </c>
       <c r="E233" t="s">
+        <v>563</v>
+      </c>
+      <c r="F233" t="s">
         <v>564</v>
-      </c>
-      <c r="F233" t="s">
-        <v>563</v>
       </c>
       <c r="G233" t="s">
         <v>564</v>
@@ -7431,10 +7431,10 @@
         <v>567</v>
       </c>
       <c r="E234" t="s">
+        <v>567</v>
+      </c>
+      <c r="F234" t="s">
         <v>568</v>
-      </c>
-      <c r="F234" t="s">
-        <v>567</v>
       </c>
       <c r="G234" t="s">
         <v>568</v>
@@ -7454,10 +7454,10 @@
         <v>567</v>
       </c>
       <c r="E235" t="s">
+        <v>567</v>
+      </c>
+      <c r="F235" t="s">
         <v>568</v>
-      </c>
-      <c r="F235" t="s">
-        <v>567</v>
       </c>
       <c r="G235" t="s">
         <v>568</v>
